--- a/AnklePositionValidation.xlsx
+++ b/AnklePositionValidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GRHRehabTech\Desktop\Kendra\AnkleDynamometer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GRHRehabTech\Documents\GitHub\AnkleDynamometer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D484F573-BA1C-46DA-A570-AD9E88F040D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D6AAF7-BD64-407F-B4B1-67B49A17E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEB06804-99E4-4814-AACA-9BD3BCB431EF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEB06804-99E4-4814-AACA-9BD3BCB431EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -253,17 +253,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5942,29 +5942,29 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" s="3"/>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
@@ -5993,7 +5993,7 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="4">
@@ -6021,7 +6021,7 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="4">
         <f>D3</f>
         <v>30</v>
@@ -6048,7 +6048,7 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="4">
         <f>E3</f>
         <v>-10</v>
@@ -6075,7 +6075,7 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4">
@@ -6103,7 +6103,7 @@
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="4">
         <f>D3</f>
         <v>30</v>
@@ -6130,7 +6130,7 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="4">
         <f>E3</f>
         <v>-10</v>
@@ -6157,31 +6157,31 @@
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>0</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H19" s="8"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
@@ -6262,18 +6262,18 @@
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
@@ -6284,7 +6284,7 @@
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="6">
+      <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" t="s">
@@ -6300,7 +6300,7 @@
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
+      <c r="B28" s="8"/>
       <c r="C28" t="s">
         <v>19</v>
       </c>
@@ -6314,7 +6314,7 @@
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
+      <c r="B29" s="8"/>
       <c r="C29" t="s">
         <v>20</v>
       </c>
@@ -6332,7 +6332,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="6">
+      <c r="B30" s="8">
         <f>D3</f>
         <v>30</v>
       </c>
@@ -6349,7 +6349,7 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="6"/>
+      <c r="B31" s="8"/>
       <c r="C31" t="s">
         <v>19</v>
       </c>
@@ -6363,7 +6363,7 @@
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
+      <c r="B32" s="8"/>
       <c r="C32" t="s">
         <v>20</v>
       </c>
@@ -6377,7 +6377,7 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="6">
+      <c r="B33" s="8">
         <f>E3</f>
         <v>-10</v>
       </c>
@@ -6394,7 +6394,7 @@
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
+      <c r="B34" s="8"/>
       <c r="C34" t="s">
         <v>19</v>
       </c>
@@ -6408,7 +6408,7 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="6"/>
+      <c r="B35" s="8"/>
       <c r="C35" t="s">
         <v>20</v>
       </c>
@@ -6422,31 +6422,31 @@
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="8">
+      <c r="C38" s="7">
         <v>0</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8">
+      <c r="D38" s="7"/>
+      <c r="E38" s="7">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8">
+      <c r="F38" s="7"/>
+      <c r="G38" s="7">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H38" s="8"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
@@ -6469,7 +6469,7 @@
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C40">
@@ -6497,7 +6497,7 @@
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="6"/>
+      <c r="B41" s="8"/>
       <c r="C41">
         <f>D27</f>
         <v>5</v>
@@ -6524,7 +6524,7 @@
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="6"/>
+      <c r="B42" s="8"/>
       <c r="C42">
         <v>10</v>
       </c>
@@ -6550,7 +6550,7 @@
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C43">
@@ -6578,7 +6578,7 @@
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="6"/>
+      <c r="B44" s="8"/>
       <c r="C44">
         <f>D29</f>
         <v>5</v>
@@ -6605,7 +6605,7 @@
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="6"/>
+      <c r="B45" s="8"/>
       <c r="C45">
         <v>10</v>
       </c>
@@ -6631,31 +6631,31 @@
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C48" s="8">
+      <c r="C48" s="7">
         <v>0</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8">
+      <c r="D48" s="7"/>
+      <c r="E48" s="7">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8">
+      <c r="F48" s="7"/>
+      <c r="G48" s="7">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H48" s="8"/>
+      <c r="H48" s="7"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
@@ -6789,11 +6789,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B24:E24"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="E48:F48"/>
@@ -6804,15 +6808,11 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/AnklePositionValidation.xlsx
+++ b/AnklePositionValidation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GRHRehabTech\Documents\GitHub\AnkleDynamometer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D6AAF7-BD64-407F-B4B1-67B49A17E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC0E371-E947-4DF2-9A87-B7F40B70801E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEB06804-99E4-4814-AACA-9BD3BCB431EF}"/>
   </bookViews>
@@ -253,17 +253,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -385,13 +385,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>-9.7644620319460795</c:v>
+                  <c:v>-9.6776379431126145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.23553796805392108</c:v>
+                  <c:v>0.32236205688738628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.23553796805392</c:v>
+                  <c:v>10.322362056887386</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -403,13 +403,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>7.2480775600968581</c:v>
+                  <c:v>7.7404814366029617</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.4848077530122081</c:v>
+                  <c:v>5.9772116295183118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7215379459275582</c:v>
+                  <c:v>4.2139418224336618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -449,13 +449,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>-10.11175838727994</c:v>
+                  <c:v>-10.198582476113405</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.11175838727993957</c:v>
+                  <c:v>-0.19858247611340474</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.8882416127200603</c:v>
+                  <c:v>9.8014175238865953</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -467,13 +467,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.2784620540724418</c:v>
+                  <c:v>4.7860581775663382</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.5151922469877919</c:v>
+                  <c:v>3.0227883704816882</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7519224399031421</c:v>
+                  <c:v>1.2595185633970385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1155,13 +1155,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>7.8301270189221945</c:v>
+                  <c:v>7.5801270189221945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.830127018922195</c:v>
+                  <c:v>17.580127018922195</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27.830127018922195</c:v>
+                  <c:v>27.580127018922195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1173,13 +1173,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>-0.40747728811181894</c:v>
+                  <c:v>2.5535413780400695E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.3660254037844384</c:v>
+                  <c:v>5.799038105676658</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.139528095680696</c:v>
+                  <c:v>11.572540797572916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,13 +1219,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8.8301270189221945</c:v>
+                  <c:v>9.0801270189221945</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.830127018922195</c:v>
+                  <c:v>19.080127018922195</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.830127018922195</c:v>
+                  <c:v>29.080127018922195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1237,13 +1237,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>-2.1395280956806961</c:v>
+                  <c:v>-2.5725407975729153</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.6339745962155612</c:v>
+                  <c:v>3.200961894323342</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.4074772881118189</c:v>
+                  <c:v>8.9744645862196002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1951,13 +1951,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2015,13 +2015,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3.5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C3" s="5">
         <v>10</v>
@@ -5942,29 +5942,29 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" s="3"/>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
@@ -5993,7 +5993,7 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="4">
@@ -6021,7 +6021,7 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="4">
         <f>D3</f>
         <v>30</v>
@@ -6048,7 +6048,7 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="8"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="4">
         <f>E3</f>
         <v>-10</v>
@@ -6075,7 +6075,7 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4">
@@ -6103,7 +6103,7 @@
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="4">
         <f>D3</f>
         <v>30</v>
@@ -6130,7 +6130,7 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="4">
         <f>E3</f>
         <v>-10</v>
@@ -6157,31 +6157,31 @@
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>0</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
@@ -6262,18 +6262,18 @@
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
@@ -6284,7 +6284,7 @@
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>0</v>
       </c>
       <c r="C27" t="s">
@@ -6296,11 +6296,11 @@
       </c>
       <c r="E27">
         <f>E28+B3</f>
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>19</v>
       </c>
@@ -6314,7 +6314,7 @@
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8"/>
+      <c r="B29" s="6"/>
       <c r="C29" t="s">
         <v>20</v>
       </c>
@@ -6324,15 +6324,15 @@
       </c>
       <c r="E29">
         <f>E28-B3</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <f>D21-D22-B3*2</f>
-        <v>-0.52</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="8">
+      <c r="B30" s="6">
         <f>D3</f>
         <v>30</v>
       </c>
@@ -6341,15 +6341,15 @@
       </c>
       <c r="D30">
         <f>D31-B3*SIN(B30*PI()/180)</f>
-        <v>17.830127018922195</v>
+        <v>17.580127018922195</v>
       </c>
       <c r="E30">
         <f>E31+B3*COS(B30*PI()/180)</f>
-        <v>5.3660254037844384</v>
+        <v>5.799038105676658</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="8"/>
+      <c r="B31" s="6"/>
       <c r="C31" t="s">
         <v>19</v>
       </c>
@@ -6363,21 +6363,21 @@
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="8"/>
+      <c r="B32" s="6"/>
       <c r="C32" t="s">
         <v>20</v>
       </c>
       <c r="D32">
         <f>D31+B3*SIN(B30*PI()/180)</f>
-        <v>18.830127018922195</v>
+        <v>19.080127018922195</v>
       </c>
       <c r="E32">
         <f>E31-B3*COS(B30*PI()/180)</f>
-        <v>3.6339745962155612</v>
+        <v>3.200961894323342</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="8">
+      <c r="B33" s="6">
         <f>E3</f>
         <v>-10</v>
       </c>
@@ -6386,15 +6386,15 @@
       </c>
       <c r="D33">
         <f>D34-B3*SIN(B33*PI()/180)</f>
-        <v>0.23553796805392108</v>
+        <v>0.32236205688738628</v>
       </c>
       <c r="E33">
         <f>E34+B3*COS(B33*PI()/180)</f>
-        <v>5.4848077530122081</v>
+        <v>5.9772116295183118</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="8"/>
+      <c r="B34" s="6"/>
       <c r="C34" t="s">
         <v>19</v>
       </c>
@@ -6408,45 +6408,45 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="8"/>
+      <c r="B35" s="6"/>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35">
         <f>D34+B3*SIN(B33*PI()/180)</f>
-        <v>-0.11175838727993957</v>
+        <v>-0.19858247611340474</v>
       </c>
       <c r="E35">
         <f>E34-B3*COS(B33*PI()/180)</f>
-        <v>3.5151922469877919</v>
+        <v>3.0227883704816882</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="7">
+      <c r="C38" s="8">
         <v>0</v>
       </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7">
+      <c r="D38" s="8"/>
+      <c r="E38" s="8">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7">
+      <c r="F38" s="8"/>
+      <c r="G38" s="8">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H38" s="7"/>
+      <c r="H38" s="8"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
@@ -6469,7 +6469,7 @@
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C40">
@@ -6477,80 +6477,80 @@
       </c>
       <c r="D40">
         <f>D41</f>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <f>E41-C3</f>
-        <v>7.8301270189221945</v>
+        <v>7.5801270189221945</v>
       </c>
       <c r="F40">
         <f>F41-$C$3*TAN(E38*PI()/180)</f>
-        <v>-0.40747728811181894</v>
+        <v>2.5535413780400695E-2</v>
       </c>
       <c r="G40">
         <f>G41-C3</f>
-        <v>-9.7644620319460795</v>
+        <v>-9.6776379431126145</v>
       </c>
       <c r="H40">
         <f>H41-$C$3*TAN(G38*PI()/180)</f>
-        <v>7.2480775600968581</v>
+        <v>7.7404814366029617</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="8"/>
+      <c r="B41" s="6"/>
       <c r="C41">
         <f>D27</f>
         <v>5</v>
       </c>
       <c r="D41">
         <f>E27</f>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <f>D30</f>
-        <v>17.830127018922195</v>
+        <v>17.580127018922195</v>
       </c>
       <c r="F41">
         <f>E30</f>
-        <v>5.3660254037844384</v>
+        <v>5.799038105676658</v>
       </c>
       <c r="G41">
         <f>D33</f>
-        <v>0.23553796805392108</v>
+        <v>0.32236205688738628</v>
       </c>
       <c r="H41">
         <f>E33</f>
-        <v>5.4848077530122081</v>
+        <v>5.9772116295183118</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
+      <c r="B42" s="6"/>
       <c r="C42">
         <v>10</v>
       </c>
       <c r="D42">
         <f>D41</f>
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E42">
         <f>E41+C3</f>
-        <v>27.830127018922195</v>
+        <v>27.580127018922195</v>
       </c>
       <c r="F42">
         <f>F41+$C$3*TAN(E38*PI()/180)</f>
-        <v>11.139528095680696</v>
+        <v>11.572540797572916</v>
       </c>
       <c r="G42">
         <f>G41+C3</f>
-        <v>10.23553796805392</v>
+        <v>10.322362056887386</v>
       </c>
       <c r="H42">
         <f>H41+$C$3*TAN(G38*PI()/180)</f>
-        <v>3.7215379459275582</v>
+        <v>4.2139418224336618</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C43">
@@ -6558,104 +6558,104 @@
       </c>
       <c r="D43">
         <f>D44</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E43">
         <f>E44-C3</f>
-        <v>8.8301270189221945</v>
+        <v>9.0801270189221945</v>
       </c>
       <c r="F43">
         <f>F44-$C$3*TAN(E38*PI()/180)</f>
-        <v>-2.1395280956806961</v>
+        <v>-2.5725407975729153</v>
       </c>
       <c r="G43">
         <f>G44-C3</f>
-        <v>-10.11175838727994</v>
+        <v>-10.198582476113405</v>
       </c>
       <c r="H43">
         <f>H44-$C$3*TAN(G38*PI()/180)</f>
-        <v>5.2784620540724418</v>
+        <v>4.7860581775663382</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="8"/>
+      <c r="B44" s="6"/>
       <c r="C44">
         <f>D29</f>
         <v>5</v>
       </c>
       <c r="D44">
         <f>E29</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <f>D32</f>
-        <v>18.830127018922195</v>
+        <v>19.080127018922195</v>
       </c>
       <c r="F44">
         <f>E32</f>
-        <v>3.6339745962155612</v>
+        <v>3.200961894323342</v>
       </c>
       <c r="G44">
         <f>D35</f>
-        <v>-0.11175838727993957</v>
+        <v>-0.19858247611340474</v>
       </c>
       <c r="H44">
         <f>E35</f>
-        <v>3.5151922469877919</v>
+        <v>3.0227883704816882</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="8"/>
+      <c r="B45" s="6"/>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45">
         <f>D44</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E45">
         <f>E44+C3</f>
-        <v>28.830127018922195</v>
+        <v>29.080127018922195</v>
       </c>
       <c r="F45">
         <f>F44+$C$3*TAN(E38*PI()/180)</f>
-        <v>9.4074772881118189</v>
+        <v>8.9744645862196002</v>
       </c>
       <c r="G45">
         <f>G44+C3</f>
-        <v>9.8882416127200603</v>
+        <v>9.8014175238865953</v>
       </c>
       <c r="H45">
         <f>H44+$C$3*TAN(G38*PI()/180)</f>
-        <v>1.7519224399031421</v>
+        <v>1.2595185633970385</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C48" s="7">
+      <c r="C48" s="8">
         <v>0</v>
       </c>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7">
+      <c r="D48" s="8"/>
+      <c r="E48" s="8">
         <f>D3</f>
         <v>30</v>
       </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7">
+      <c r="F48" s="8"/>
+      <c r="G48" s="8">
         <f>E3</f>
         <v>-10</v>
       </c>
-      <c r="H48" s="7"/>
+      <c r="H48" s="8"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
@@ -6789,15 +6789,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="E48:F48"/>
@@ -6808,11 +6804,15 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/AnklePositionValidation.xlsx
+++ b/AnklePositionValidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GRHRehabTech\Documents\GitHub\AnkleDynamometer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC0E371-E947-4DF2-9A87-B7F40B70801E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F461C658-12D8-45B6-AB04-6A416A8A6945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEB06804-99E4-4814-AACA-9BD3BCB431EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEB06804-99E4-4814-AACA-9BD3BCB431EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1131,7 +1131,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Upper Bounds</c:v>
+            <c:v>95% Upper Bound</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1195,7 +1195,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Lower Bounds</c:v>
+            <c:v>95% Lower Bound</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1323,7 +1323,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1781,6 +1781,49 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.64938957583496137"/>
+          <c:y val="0.17948709650711825"/>
+          <c:w val="0.26311307233784237"/>
+          <c:h val="0.34678388264163124"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5407,16 +5450,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>149597</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>121022</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>329451</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
